--- a/performance_historique.xlsx
+++ b/performance_historique.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,77 +417,77 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Mois</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Année</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>CA réalisé global (€)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>CA LITTERALIS (€)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>CA GEODP (€)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Objectif global (€)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>% Atteinte objectif</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>CA N-1 global (€)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Évolution N/N-1 (%)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Rentabilité globale (€/h)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Nb projets travaillés</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Nb projets avec CA</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Nb jours ouvrés</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Jours écoulés</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>% Avancement calendaire</t>
         </is>
@@ -775,10 +763,10 @@
         <v>-72.59999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>184.14</v>
+        <v>172.34</v>
       </c>
       <c r="K7" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="L7" t="n">
         <v>48</v>
@@ -787,10 +775,10 @@
         <v>22</v>
       </c>
       <c r="N7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O7" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/performance_historique.xlsx
+++ b/performance_historique.xlsx
@@ -763,7 +763,7 @@
         <v>-72.59999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>172.34</v>
+        <v>171.07</v>
       </c>
       <c r="K7" t="n">
         <v>122</v>

--- a/performance_historique.xlsx
+++ b/performance_historique.xlsx
@@ -742,10 +742,10 @@
         <v>2026</v>
       </c>
       <c r="C7" t="n">
-        <v>35066.73</v>
+        <v>35469.48</v>
       </c>
       <c r="D7" t="n">
-        <v>9868.1</v>
+        <v>10270.85</v>
       </c>
       <c r="E7" t="n">
         <v>25198.63</v>
@@ -754,19 +754,19 @@
         <v>120460</v>
       </c>
       <c r="G7" t="n">
-        <v>29.1</v>
+        <v>29.4</v>
       </c>
       <c r="H7" t="n">
         <v>128013</v>
       </c>
       <c r="I7" t="n">
-        <v>-72.59999999999999</v>
+        <v>-72.3</v>
       </c>
       <c r="J7" t="n">
-        <v>171.07</v>
+        <v>166.73</v>
       </c>
       <c r="K7" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L7" t="n">
         <v>48</v>
